--- a/artfynd/A 18399-2026 artfynd.xlsx
+++ b/artfynd/A 18399-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>91605077</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543527.3784509068</v>
+        <v>543527</v>
       </c>
       <c r="R2" t="n">
-        <v>6301438.775133566</v>
+        <v>6301439</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -796,6 +791,372 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>14946191</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5471</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>101377</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stekelbock</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Necydalis major</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Orrefors Hälleskog 13B, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>543478</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6301361</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hälleberga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2011-06-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2011-08-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inventering för Sveaskog</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Högstubbe björk</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Bengt Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bengt Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>15694889</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5471</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>101377</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stekelbock</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Necydalis major</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hälleskog 13B, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>543478</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6301362</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hälleberga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2013-07-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Björk-högstubbe. Inventering för Sveaskog.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bengt Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bengt Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>15245145</v>
+      </c>
+      <c r="B5" t="n">
+        <v>9178</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101595</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Aspstumpbagge</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platysoma deplanatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Gyllenhal, 1808)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hälleskog 13T, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>543478</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6301362</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hälleberga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2012-06-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2012-07-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tall-högstubbe. Inventering för Sveaskog.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bengt Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bengt Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18399-2026 artfynd.xlsx
+++ b/artfynd/A 18399-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91605077</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,6 +923,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14946191</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15694889</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1157,8 +1177,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15245145</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>